--- a/artfynd/S 862-2020 artfynd.xlsx
+++ b/artfynd/S 862-2020 artfynd.xlsx
@@ -7671,7 +7671,7 @@
         <v>136438438</v>
       </c>
       <c r="B68" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136438441</v>
       </c>
       <c r="B78" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>136438443</v>
       </c>
       <c r="B79" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 862-2020 artfynd.xlsx
+++ b/artfynd/S 862-2020 artfynd.xlsx
@@ -7671,7 +7671,7 @@
         <v>136438438</v>
       </c>
       <c r="B68" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136438441</v>
       </c>
       <c r="B78" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>136438443</v>
       </c>
       <c r="B79" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 862-2020 artfynd.xlsx
+++ b/artfynd/S 862-2020 artfynd.xlsx
@@ -7671,7 +7671,7 @@
         <v>136438438</v>
       </c>
       <c r="B68" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136438441</v>
       </c>
       <c r="B78" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>136438443</v>
       </c>
       <c r="B79" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 862-2020 artfynd.xlsx
+++ b/artfynd/S 862-2020 artfynd.xlsx
@@ -7671,7 +7671,7 @@
         <v>136438438</v>
       </c>
       <c r="B68" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136438441</v>
       </c>
       <c r="B78" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>136438443</v>
       </c>
       <c r="B79" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 862-2020 artfynd.xlsx
+++ b/artfynd/S 862-2020 artfynd.xlsx
@@ -7671,7 +7671,7 @@
         <v>136438438</v>
       </c>
       <c r="B68" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136438441</v>
       </c>
       <c r="B78" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>136438443</v>
       </c>
       <c r="B79" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 862-2020 artfynd.xlsx
+++ b/artfynd/S 862-2020 artfynd.xlsx
@@ -7671,7 +7671,7 @@
         <v>136438438</v>
       </c>
       <c r="B68" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136438441</v>
       </c>
       <c r="B78" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>136438443</v>
       </c>
       <c r="B79" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 862-2020 artfynd.xlsx
+++ b/artfynd/S 862-2020 artfynd.xlsx
@@ -7671,7 +7671,7 @@
         <v>136438438</v>
       </c>
       <c r="B68" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136438441</v>
       </c>
       <c r="B78" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>136438443</v>
       </c>
       <c r="B79" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
